--- a/esyluban/examples/dev/DataTables/test/field_variant/a1.xlsx
+++ b/esyluban/examples/dev/DataTables/test/field_variant/a1.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1">
@@ -434,7 +434,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbTestFieldVariant" &amp; value_type="test.TestFieldVariant" &amp; read_schema_from_file="false" &amp; input="test/field_variant" &amp; output="test_tbtestfieldvariant"</t>
+          <t>full_name="test.TbTestFieldVariant" &amp; input="test/field_variant"</t>
         </is>
       </c>
       <c r="D1" s="0" t="inlineStr">
@@ -582,18 +582,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId1"/>
